--- a/Portfolio_Tracker.xlsx
+++ b/Portfolio_Tracker.xlsx
@@ -8,16 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Azioni" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ETF" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Bond" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Fondi Comuni" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Conti &amp; Liquidità" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Mutuo &amp; Debiti" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Stipendi" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Spese Mensili" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Tasse" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Storico Patrimonio" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Investimenti" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Fondi Comuni" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Conti &amp; Liquidità" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mutuo &amp; Debiti" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Stipendi" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Spese Mensili" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Tasse" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Storico Patrimonio" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,8 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="€#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;%&quot;"/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,7 +38,54 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="24"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0010B981"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00EF4444"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00EF4444"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,10 +93,53 @@
       <sz val="11"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="009CA3AF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
+      <color rgb="003B82F6"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="004B5563"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00EF4444"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="003B82F6"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00F59E0B"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -57,12 +148,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="001E3A8A"/>
+        <bgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F4F6"/>
+        <bgColor rgb="00F3F4F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE9FE"/>
+        <bgColor rgb="00EDE9FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F2937"/>
+        <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9FAFB"/>
+        <bgColor rgb="00F9FAFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -71,25 +210,109 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right style="medium">
+        <color rgb="001E3A8A"/>
+      </right>
+      <top style="medium">
+        <color rgb="001E3A8A"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001E3A8A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="19" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -455,326 +678,238 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RIEPILOGO PATRIMONIO</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr"/>
+          <t>PORTFOLIO TRACKER</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ultimo aggiornamento: 23/11/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="10" customHeight="1"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>PATRIMONIO NETTO</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>TOTALE ATTIVO</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>TOTALE PASSIVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="35" customHeight="1">
+      <c r="A5" s="6">
+        <f>B15-B17</f>
+        <v/>
+      </c>
+      <c r="D5" s="7">
+        <f>B15</f>
+        <v/>
+      </c>
+      <c r="F5" s="8">
+        <f>B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1"/>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>COMPOSIZIONE PORTAFOGLIO</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>📊 INSERISCI QUI IL GRAFICO A TORTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Valore (€)</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Azioni</t>
-        </is>
-      </c>
-      <c r="B4">
-        <f>SUMIF(Azioni!A:A,"&lt;&gt;",Azioni!H:H)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ETF</t>
-        </is>
-      </c>
-      <c r="B5">
-        <f>SUMIF(ETF!A:A,"&lt;&gt;",ETF!H:H)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Bond</t>
-        </is>
-      </c>
-      <c r="B6">
-        <f>SUMIF(Bond!A:A,"&lt;&gt;",Bond!G:G)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>% Portafoglio</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Seleziona i dati A9:B14
+e inserisci un grafico a torta
+(Inserisci → Grafico → Torta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Investimenti</t>
+        </is>
+      </c>
+      <c r="B9" s="14">
+        <f>SUMIF(Investimenti!B:B,"&lt;&gt;",Investimenti!I:I)</f>
+        <v/>
+      </c>
+      <c r="C9" s="15">
+        <f>IF($B$15&gt;0,B9/$B$15*100,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Fondi Comuni</t>
         </is>
       </c>
-      <c r="B7">
+      <c r="B10" s="14">
         <f>SUMIF('Fondi Comuni'!A:A,"&lt;&gt;",'Fondi Comuni'!F:F)</f>
         <v/>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="C10" s="15">
+        <f>IF($B$15&gt;0,B10/$B$15*100,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Conti &amp; Liquidità</t>
         </is>
       </c>
-      <c r="B8">
+      <c r="B11" s="14">
         <f>SUMIF('Conti &amp; Liquidità'!A:A,"&lt;&gt;",'Conti &amp; Liquidità'!C:C)</f>
         <v/>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="C11" s="15">
+        <f>IF($B$15&gt;0,B11/$B$15*100,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>DETTAGLIO INVESTIMENTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Azioni</t>
+        </is>
+      </c>
+      <c r="B14" s="18">
+        <f>SUMIFS(Investimenti!I:I,Investimenti!A:A,"Azione")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • ETF</t>
+        </is>
+      </c>
+      <c r="B15" s="18">
+        <f>SUMIFS(Investimenti!I:I,Investimenti!A:A,"ETF")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Bond</t>
+        </is>
+      </c>
+      <c r="B16" s="18">
+        <f>SUMIFS(Investimenti!I:I,Investimenti!A:A,"Bond")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>TOTALE ATTIVO</t>
         </is>
       </c>
-      <c r="B9" s="3">
-        <f>SUM(B4:B8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="B17" s="20">
+        <f>SUM(B9:B11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>Mutuo &amp; Debiti</t>
         </is>
       </c>
-      <c r="B11">
+      <c r="B19" s="22">
         <f>SUMIF('Mutuo &amp; Debiti'!A:A,"&lt;&gt;",'Mutuo &amp; Debiti'!C:C)</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>TOTALE PASSIVO</t>
-        </is>
-      </c>
-      <c r="B12" s="3">
-        <f>B11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>PATRIMONIO NETTO</t>
         </is>
       </c>
-      <c r="B14" s="3">
-        <f>B9-B12</f>
+      <c r="B21" s="24">
+        <f>B15-B17</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Anno Fiscale</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Descrizione</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Base Imponibile (€)</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Aliquota (%)</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Importo Pagato (€)</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Data Pagamento</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Capital Gain</t>
-        </is>
-      </c>
-      <c r="F2">
-        <f>IF(D2&lt;&gt;"",D2*(E2/100),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Dividendi</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Interessi</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Azioni</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>ETF</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Bond</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Fondi</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Liquidità</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Totale Attivo</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Debiti</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Patrimonio Netto</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>Var. % Mensile</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="G2">
-        <f>SUM(B2:F2)</f>
-        <v/>
-      </c>
-      <c r="I2">
-        <f>G2-H2</f>
-        <v/>
-      </c>
-      <c r="J2">
-        <f>IF(I1&lt;&gt;0,(I2-I1)/I1*100,"")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="D8:F20"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D7:F7"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -785,105 +920,136 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="25" t="inlineStr">
+        <is>
+          <t>Ticker/ISIN</t>
+        </is>
+      </c>
+      <c r="C1" s="25" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Quantità</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="25" t="inlineStr">
+        <is>
+          <t>Quantità/Nominale</t>
+        </is>
+      </c>
+      <c r="E1" s="25" t="inlineStr">
         <is>
           <t>Prezzo Carico (€)</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="25" t="inlineStr">
         <is>
           <t>Prezzo Corrente (€)</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="25" t="inlineStr">
         <is>
           <t>Valore Carico (€)</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="25" t="inlineStr">
         <is>
           <t>Valore Corrente (€)</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="25" t="inlineStr">
         <is>
           <t>P&amp;L (€)</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="25" t="inlineStr">
         <is>
           <t>P&amp;L (%)</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>Dividendi Ricevuti (€)</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="25" t="inlineStr">
+        <is>
+          <t>Dividendi/Cedole (€)</t>
+        </is>
+      </c>
+      <c r="L1" s="25" t="inlineStr">
         <is>
           <t>Data Acquisto</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="25" t="inlineStr">
+        <is>
+          <t>Scadenza</t>
+        </is>
+      </c>
+      <c r="N1" s="25" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="E2">
-        <f>IFERROR(GOOGLEFINANCE(A2,"price"),"")</f>
-        <v/>
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>Azione</t>
+        </is>
       </c>
       <c r="F2">
-        <f>IF(C2&lt;&gt;"",C2*D2,"")</f>
+        <f>IF(A2="Bond","",IFERROR(GOOGLEFINANCE(B2,"price"),""))</f>
         <v/>
       </c>
       <c r="G2">
-        <f>IF(C2&lt;&gt;"",C2*E2,"")</f>
+        <f>IF(D2&lt;&gt;"",D2*E2,"")</f>
         <v/>
       </c>
       <c r="H2">
-        <f>IF(G2&lt;&gt;"",G2-F2,"")</f>
+        <f>IF(AND(D2&lt;&gt;"",F2&lt;&gt;""),D2*F2,"")</f>
         <v/>
       </c>
       <c r="I2">
-        <f>IF(F2&lt;&gt;0,H2/F2*100,"")</f>
-        <v/>
+        <f>IF(H2&lt;&gt;"",H2-G2,"")</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>IF(G2&lt;&gt;0,I2/G2*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="27" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -892,208 +1058,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Nome</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Quantità</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Prezzo Carico (€)</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Prezzo Corrente (€)</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Valore Carico (€)</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Valore Corrente (€)</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>P&amp;L (€)</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>P&amp;L (%)</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>Dividendi Ricevuti (€)</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>Data Acquisto</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="E2">
-        <f>IFERROR(GOOGLEFINANCE(A2,"price"),"")</f>
-        <v/>
-      </c>
-      <c r="F2">
-        <f>IF(C2&lt;&gt;"",C2*D2,"")</f>
-        <v/>
-      </c>
-      <c r="G2">
-        <f>IF(C2&lt;&gt;"",C2*E2,"")</f>
-        <v/>
-      </c>
-      <c r="H2">
-        <f>IF(G2&lt;&gt;"",G2-F2,"")</f>
-        <v/>
-      </c>
-      <c r="I2">
-        <f>IF(F2&lt;&gt;0,H2/F2*100,"")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Nome/ISIN</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Valore Nominale (€)</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Prezzo Acquisto (%)</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Data Acquisto</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Scadenza</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Cedola (%)</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Frequenza Cedole</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Valore Corrente (€)</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Rendimento YTM (%)</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>Cedole Incassate (€)</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="H2">
-        <f>IF(B2&lt;&gt;"",B2*(C2/100),"")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1115,52 +1079,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>Nome Fondo</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>ISIN</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="25" t="inlineStr">
         <is>
           <t>Quote</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="25" t="inlineStr">
         <is>
           <t>Prezzo Carico (€)</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="25" t="inlineStr">
         <is>
           <t>Prezzo Corrente (€)</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="25" t="inlineStr">
         <is>
           <t>Valore Corrente (€)</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="25" t="inlineStr">
         <is>
           <t>P&amp;L (€)</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="25" t="inlineStr">
         <is>
           <t>P&amp;L (%)</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="25" t="inlineStr">
         <is>
           <t>Data Acquisto</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="25" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -1185,7 +1149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1204,37 +1168,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>Nome Conto/Banca</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="25" t="inlineStr">
         <is>
           <t>Saldo (€)</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="25" t="inlineStr">
         <is>
           <t>Tasso Interesse (%)</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="25" t="inlineStr">
         <is>
           <t>Scadenza Vincolo</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="25" t="inlineStr">
         <is>
           <t>Interessi Maturati (€)</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="25" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -1266,7 +1230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1286,42 +1250,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>Tipo Debito</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>Importo Iniziale (€)</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="25" t="inlineStr">
         <is>
           <t>Debito Residuo (€)</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="25" t="inlineStr">
         <is>
           <t>Tasso Interesse (%)</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="25" t="inlineStr">
         <is>
           <t>Rata Mensile (€)</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="25" t="inlineStr">
         <is>
           <t>Data Inizio</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="25" t="inlineStr">
         <is>
           <t>Scadenza</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="25" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -1332,7 +1296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1351,37 +1315,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>Anno</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>Mese</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="25" t="inlineStr">
         <is>
           <t>Stipendio Lordo (€)</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="25" t="inlineStr">
         <is>
           <t>Stipendio Netto (€)</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="25" t="inlineStr">
         <is>
           <t>Bonus/Extra (€)</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="25" t="inlineStr">
         <is>
           <t>Totale Netto (€)</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="25" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -1516,7 +1480,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1540,62 +1504,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>Anno</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>Mese</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="25" t="inlineStr">
         <is>
           <t>Affitto/Mutuo (€)</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="25" t="inlineStr">
         <is>
           <t>Bollette (€)</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="25" t="inlineStr">
         <is>
           <t>Spesa (€)</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="25" t="inlineStr">
         <is>
           <t>Trasporti (€)</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="25" t="inlineStr">
         <is>
           <t>Assicurazioni (€)</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="25" t="inlineStr">
         <is>
           <t>Abbonamenti (€)</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="25" t="inlineStr">
         <is>
           <t>Svago (€)</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="25" t="inlineStr">
         <is>
           <t>Altro (€)</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="25" t="inlineStr">
         <is>
           <t>TOTALE (€)</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="25" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -1723,6 +1687,177 @@
         <is>
           <t>Dicembre</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Anno Fiscale</t>
+        </is>
+      </c>
+      <c r="B1" s="25" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="C1" s="25" t="inlineStr">
+        <is>
+          <t>Descrizione</t>
+        </is>
+      </c>
+      <c r="D1" s="25" t="inlineStr">
+        <is>
+          <t>Base Imponibile (€)</t>
+        </is>
+      </c>
+      <c r="E1" s="25" t="inlineStr">
+        <is>
+          <t>Aliquota (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="25" t="inlineStr">
+        <is>
+          <t>Importo Pagato (€)</t>
+        </is>
+      </c>
+      <c r="G1" s="25" t="inlineStr">
+        <is>
+          <t>Data Pagamento</t>
+        </is>
+      </c>
+      <c r="H1" s="25" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Capital Gain</t>
+        </is>
+      </c>
+      <c r="F2">
+        <f>IF(D2&lt;&gt;"",D2*(E2/100),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dividendi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Interessi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="25" t="inlineStr">
+        <is>
+          <t>Investimenti</t>
+        </is>
+      </c>
+      <c r="C1" s="25" t="inlineStr">
+        <is>
+          <t>Fondi</t>
+        </is>
+      </c>
+      <c r="D1" s="25" t="inlineStr">
+        <is>
+          <t>Liquidità</t>
+        </is>
+      </c>
+      <c r="E1" s="25" t="inlineStr">
+        <is>
+          <t>Totale Attivo</t>
+        </is>
+      </c>
+      <c r="F1" s="25" t="inlineStr">
+        <is>
+          <t>Debiti</t>
+        </is>
+      </c>
+      <c r="G1" s="25" t="inlineStr">
+        <is>
+          <t>Patrimonio Netto</t>
+        </is>
+      </c>
+      <c r="H1" s="25" t="inlineStr">
+        <is>
+          <t>Var. % Mensile</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="E2">
+        <f>SUM(B2:D2)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>E2-F2</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>IF(G1&lt;&gt;0,(G2-G1)/G1*100,"")</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/Portfolio_Tracker.xlsx
+++ b/Portfolio_Tracker.xlsx
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1017,6 +1017,18 @@
           <t>Azione</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2">
         <f>IF(A2="Bond","",IFERROR(GOOGLEFINANCE(B2,"price"),""))</f>
         <v/>
@@ -1037,20 +1049,315 @@
         <f>IF(G2&lt;&gt;0,I2/G2*100,"")</f>
         <v/>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="27" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>Azione</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIT:ENI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Eni S.p.A.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3">
+        <f>IF(A3="Bond","",IFERROR(GOOGLEFINANCE(B3,"price"),""))</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>IF(D3&lt;&gt;"",D3*E3,"")</f>
+        <v/>
+      </c>
+      <c r="H3">
+        <f>IF(AND(D3&lt;&gt;"",F3&lt;&gt;""),D3*F3,"")</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3&lt;&gt;"",H3-G3,"")</f>
+        <v/>
+      </c>
+      <c r="J3">
+        <f>IF(G3&lt;&gt;0,I3/G3*100,"")</f>
+        <v/>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>Azione</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIT:UCG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>UniCredit</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4">
+        <f>IF(A4="Bond","",IFERROR(GOOGLEFINANCE(B4,"price"),""))</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>IF(D4&lt;&gt;"",D4*E4,"")</f>
+        <v/>
+      </c>
+      <c r="H4">
+        <f>IF(AND(D4&lt;&gt;"",F4&lt;&gt;""),D4*F4,"")</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4&lt;&gt;"",H4-G4,"")</f>
+        <v/>
+      </c>
+      <c r="J4">
+        <f>IF(G4&lt;&gt;0,I4/G4*100,"")</f>
+        <v/>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5">
+        <f>IF(A5="Bond","",IFERROR(GOOGLEFINANCE(B5,"price"),""))</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>IF(D5&lt;&gt;"",D5*E5,"")</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>IF(AND(D5&lt;&gt;"",F5&lt;&gt;""),D5*F5,"")</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5&lt;&gt;"",H5-G5,"")</f>
+        <v/>
+      </c>
+      <c r="J5">
+        <f>IF(G5&lt;&gt;0,I5/G5*100,"")</f>
+        <v/>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EPA:IWDA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI World</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6">
+        <f>IF(A6="Bond","",IFERROR(GOOGLEFINANCE(B6,"price"),""))</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>IF(D6&lt;&gt;"",D6*E6,"")</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>IF(AND(D6&lt;&gt;"",F6&lt;&gt;""),D6*F6,"")</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6&lt;&gt;"",H6-G6,"")</f>
+        <v/>
+      </c>
+      <c r="J6">
+        <f>IF(G6&lt;&gt;0,I6/G6*100,"")</f>
+        <v/>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AMS:VWCE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Vanguard FTSE All-World</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7">
+        <f>IF(A7="Bond","",IFERROR(GOOGLEFINANCE(B7,"price"),""))</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>IF(D7&lt;&gt;"",D7*E7,"")</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>IF(AND(D7&lt;&gt;"",F7&lt;&gt;""),D7*F7,"")</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7&lt;&gt;"",H7-G7,"")</f>
+        <v/>
+      </c>
+      <c r="J7">
+        <f>IF(G7&lt;&gt;0,I7/G7*100,"")</f>
+        <v/>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Bond</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IT0005423745</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BTP Italia 2030</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8">
+        <f>IF(A8="Bond","",IFERROR(GOOGLEFINANCE(B8,"price"),""))</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IF(D8&lt;&gt;"",D8*E8,"")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>IF(AND(D8&lt;&gt;"",F8&lt;&gt;""),D8*F8,"")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8&lt;&gt;"",H8-G8,"")</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>IF(G8&lt;&gt;0,I8/G8*100,"")</f>
+        <v/>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>31/12/2030</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BTP 2.5% 2033</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9">
+        <f>IF(A9="Bond","",IFERROR(GOOGLEFINANCE(B9,"price"),""))</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>IF(D9&lt;&gt;"",D9*E9,"")</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>IF(AND(D9&lt;&gt;"",F9&lt;&gt;""),D9*F9,"")</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9&lt;&gt;"",H9-G9,"")</f>
+        <v/>
+      </c>
+      <c r="J9">
+        <f>IF(G9&lt;&gt;0,I9/G9*100,"")</f>
+        <v/>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>01/12/2033</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
